--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:03:58+00:00</t>
+    <t>2025-05-14T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="192">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -557,6 +557,9 @@
   </si>
   <si>
     <t>HealthCareFacility.code.translation.code</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j368-categorie-etablissement-cisis</t>
   </si>
   <si>
     <t>HealthCareFacility.code.translation.codeSystem</t>
@@ -3761,13 +3764,11 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3805,10 +3806,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3908,10 +3909,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4011,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4114,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4217,10 +4218,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4318,10 +4319,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4419,10 +4420,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4522,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4625,10 +4626,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4728,10 +4729,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4754,10 +4755,10 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -4809,7 +4810,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4829,10 +4830,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4855,7 +4856,7 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -4908,7 +4909,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
